--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-dentaloral-ecs.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-dentaloral-ecs.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -377,7 +377,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -519,7 +519,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -590,7 +590,7 @@
     <t>これは、検索、並べ替え、および表示の目的で使用される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS|1.1.0</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -830,7 +830,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS|1.1.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -852,7 +852,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -885,7 +885,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -981,7 +981,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1027,7 +1027,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1051,7 +1051,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_DentalOral_eCS)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_DentalOral_eCS|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1074,7 +1074,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy)
+    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -1156,7 +1156,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.0.1)
 </t>
   </si>
   <si>
@@ -1208,7 +1208,7 @@
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1547,7 +1547,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="160.03515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="188.53515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1562,7 +1562,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-dentaloral-ecs.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-dentaloral-ecs.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -377,7 +377,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -519,7 +519,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
 </t>
   </si>
   <si>
@@ -590,7 +590,7 @@
     <t>これは、検索、並べ替え、および表示の目的で使用される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -830,7 +830,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -852,7 +852,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -885,7 +885,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -981,7 +981,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam)
 </t>
   </si>
   <si>
@@ -1027,7 +1027,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1051,7 +1051,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_DentalOral_eCS|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_DentalOral_eCS)
 </t>
   </si>
   <si>
@@ -1074,7 +1074,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(ImagingStudy)
 </t>
   </si>
   <si>
@@ -1156,7 +1156,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media|4.0.1)
+    <t xml:space="preserve">Reference(Media)
 </t>
   </si>
   <si>
@@ -1208,7 +1208,7 @@
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1547,7 +1547,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="188.53515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="160.03515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1562,7 +1562,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
